--- a/var/data/original_files/Articles A August 31.xlsx
+++ b/var/data/original_files/Articles A August 31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,11 +488,6 @@
           <t>Full Link</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Coordinates</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -544,11 +539,6 @@
           <t>https://www.nucnet.org/news/us-doe-announces-significant-step-in-strengthening-nuclear-fuel-supply-chains-8-1-2025</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>(38.8950368, -77.0365427)</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -600,11 +590,6 @@
           <t>https://www.cidrap.umn.edu/chikungunya/fda-suspends-license-chikungunya-vaccine-ixchiq-over-serious-safety-concerns</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>(39.5162401, -76.9382069)</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -656,11 +641,6 @@
           <t>https://www.cidrap.umn.edu/measles/indonesia-reports-17-deaths-measles-outbreak-launches-vaccine-drive</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>(-6.1754049, 106.827168)</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -699,7 +679,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -710,11 +690,6 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>https://www.aa.com.tr/en/asia-pacific/japan-releases-3rd-round-of-treated-nuclear-waste-into-sea/3668503</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>(35.9263502, 136.6068127)</t>
         </is>
       </c>
     </row>
@@ -768,7 +743,6 @@
           <t>https://trt.global/world/article/6883d0efec54</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -820,11 +794,6 @@
           <t>https://thesun.my/world-news/north-korea-could-produce-10-to-20-nuclear-weapons-per-year-FE14762263</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>(39.0167979, 125.7473609)</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -876,11 +845,6 @@
           <t>https://www.frontiersin.org/journals/veterinary-science/articles/10.3389/fvets.2025.1648695/abstract</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>(55.6867243, 12.5700724)</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -932,11 +896,6 @@
           <t>https://www.bta.bg/en/news/bulgaria/954164-sheep-pox-detected-in-village-near-svilengrad</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>(41.7681668, 26.1978704)</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -988,11 +947,6 @@
           <t>https://www.who.int/publications/i/item/9789240112285</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>(46.2017559, 6.1466014)</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1044,11 +998,6 @@
           <t>https://www.cidrap.umn.edu/covid-19/us-covid-19-levels-continue-climb-gradually</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>(39.5162401, -76.9382069)</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1100,11 +1049,6 @@
           <t>https://www.nyc.gov/site/doh/health/health-topics/legionnaires-disease.page</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>(40.7127281, -74.0060152)</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1156,11 +1100,6 @@
           <t>https://www.cidrap.umn.edu/chikungunya/paho-sounds-alert-local-chikungunya-outbreaks-expanded-oropouche-spread</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>(38.8950368, -77.0365427)</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1212,11 +1151,6 @@
           <t>https://www.cidrap.umn.edu/adult-non-flu-vaccines/acip-review-covid-hep-b-and-mmrv-vaccine-recommendations-september-meeting</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>(33.7544657, -84.3898151)</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1268,11 +1202,6 @@
           <t>https://globalbiodefense.com/2025/08/31/asia-wildlife-spillover-woah-surveillance-report/</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>(48.9759637, 2.1998877)</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1324,11 +1253,6 @@
           <t>https://globalbiodefense.com/2025/08/29/genomics-us-public-health-surveillance/</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>(39.5162401, -76.9382069)</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1380,7 +1304,6 @@
           <t>https://www.thenationalnews.com/news/europe/2025/08/28/european-powers-trigger-snapback-nuclear-sanctions-on-iran/</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1432,11 +1355,6 @@
           <t>https://www.azernews.az/region/246737.html</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>(40.7127281, -74.0060152)</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1488,7 +1406,6 @@
           <t>https://www.aljazeera.com/news/2025/8/29/russia-china-slam-european-nations-over-iran-snapback-sanctions-move</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1540,7 +1457,6 @@
           <t>https://www.middleeastmonitor.com/20250829-iran-drafts-urgent-bill-to-withdraw-from-nuclear-treaty/</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1592,11 +1508,6 @@
           <t>https://abcnews.go.com/Health/fda-expands-warning-radioactive-shrimp-2-brands-recalled/story?id=125104448</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>(39.5162401, -76.9382069)</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1648,7 +1559,6 @@
           <t>https://english.varthabharati.in/world/al-shifa-hospital-director-warns-of-emergence-of-new-virus-in-gaza</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1698,11 +1608,6 @@
       <c r="K23" t="inlineStr">
         <is>
           <t>https://gulfnews.com/world/mena/gas-line-explosion-in-egypts-ismailia-kills-two-injures-nine-1.500251985</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>(30.6043775, 32.2770825)</t>
         </is>
       </c>
     </row>
